--- a/5/search/FY3_Missile1_results/top10_solutions.xlsx
+++ b/5/search/FY3_Missile1_results/top10_solutions.xlsx
@@ -487,34 +487,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90</v>
+        <v>76.5</v>
       </c>
       <c r="B2" t="n">
-        <v>128.8</v>
+        <v>112</v>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>6000</v>
+        <v>6732.084661052119</v>
       </c>
       <c r="F2" t="n">
-        <v>-424</v>
+        <v>49.35207036711381</v>
       </c>
       <c r="G2" t="n">
         <v>700</v>
       </c>
       <c r="H2" t="n">
-        <v>6000</v>
+        <v>6732.084661052119</v>
       </c>
       <c r="I2" t="n">
-        <v>91.20000000000005</v>
+        <v>49.35207036711381</v>
       </c>
       <c r="J2" t="n">
-        <v>621.6</v>
+        <v>700</v>
       </c>
       <c r="K2" t="n">
         <v>3</v>
@@ -522,34 +522,34 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>90</v>
+        <v>76.5</v>
       </c>
       <c r="B3" t="n">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="C3" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>6000</v>
+        <v>6683.528025370091</v>
       </c>
       <c r="F3" t="n">
-        <v>-312</v>
+        <v>-152.9008730756032</v>
       </c>
       <c r="G3" t="n">
         <v>700</v>
       </c>
       <c r="H3" t="n">
-        <v>6000</v>
+        <v>6740.488694150932</v>
       </c>
       <c r="I3" t="n">
-        <v>24</v>
+        <v>84.35738750142991</v>
       </c>
       <c r="J3" t="n">
-        <v>621.6</v>
+        <v>680.4</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -557,37 +557,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>81</v>
+        <v>76.5</v>
       </c>
       <c r="B4" t="n">
-        <v>78.40000000000001</v>
+        <v>132</v>
       </c>
       <c r="C4" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>6441.520634129548</v>
+        <v>6739.554912695508</v>
       </c>
       <c r="F4" t="n">
-        <v>-212.3484275042829</v>
+        <v>80.46790781983918</v>
       </c>
       <c r="G4" t="n">
         <v>700</v>
       </c>
       <c r="H4" t="n">
-        <v>6478.314020307011</v>
+        <v>6739.554912695508</v>
       </c>
       <c r="I4" t="n">
-        <v>19.95587020369356</v>
+        <v>80.46790781983918</v>
       </c>
       <c r="J4" t="n">
-        <v>655.9</v>
+        <v>700</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -595,174 +595,174 @@
         <v>81</v>
       </c>
       <c r="B5" t="n">
-        <v>89.59999999999999</v>
+        <v>128</v>
       </c>
       <c r="C5" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>6448.52889816335</v>
+        <v>6480.566676603589</v>
       </c>
       <c r="F5" t="n">
-        <v>-168.0999898456212</v>
+        <v>34.17858230826323</v>
       </c>
       <c r="G5" t="n">
         <v>700</v>
       </c>
       <c r="H5" t="n">
-        <v>6476.56195429856</v>
+        <v>6480.566676603589</v>
       </c>
       <c r="I5" t="n">
-        <v>8.89376078902751</v>
+        <v>34.17858230826323</v>
       </c>
       <c r="J5" t="n">
-        <v>680.4</v>
+        <v>700</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="B6" t="n">
-        <v>134.4</v>
+        <v>110</v>
       </c>
       <c r="C6" t="n">
         <v>24</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>3719.156366604673</v>
+        <v>6000</v>
       </c>
       <c r="F6" t="n">
-        <v>-719.1563666046723</v>
+        <v>-360</v>
       </c>
       <c r="G6" t="n">
         <v>700</v>
       </c>
       <c r="H6" t="n">
-        <v>2863.840004081426</v>
+        <v>6000</v>
       </c>
       <c r="I6" t="n">
-        <v>136.1599959185756</v>
+        <v>80</v>
       </c>
       <c r="J6" t="n">
-        <v>303.1</v>
+        <v>621.6</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>81</v>
+        <v>94.5</v>
       </c>
       <c r="B7" t="n">
-        <v>109.2</v>
+        <v>128</v>
       </c>
       <c r="C7" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>6478.31402030701</v>
+        <v>5799.144714936717</v>
       </c>
       <c r="F7" t="n">
-        <v>19.95587020369294</v>
+        <v>-447.8916256431926</v>
       </c>
       <c r="G7" t="n">
         <v>700</v>
       </c>
       <c r="H7" t="n">
-        <v>6478.31402030701</v>
+        <v>5758.97365792406</v>
       </c>
       <c r="I7" t="n">
-        <v>19.95587020369294</v>
+        <v>62.53004922816893</v>
       </c>
       <c r="J7" t="n">
-        <v>700</v>
+        <v>621.6</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>90</v>
+        <v>103.5</v>
       </c>
       <c r="B8" t="n">
-        <v>75.59999999999999</v>
+        <v>126</v>
       </c>
       <c r="C8" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>6000</v>
+        <v>5411.717683083119</v>
       </c>
       <c r="F8" t="n">
-        <v>-278.4000000000001</v>
+        <v>-549.6278005978547</v>
       </c>
       <c r="G8" t="n">
         <v>700</v>
       </c>
       <c r="H8" t="n">
-        <v>6000</v>
+        <v>5264.647103853898</v>
       </c>
       <c r="I8" t="n">
-        <v>23.99999999999989</v>
+        <v>62.96524925268159</v>
       </c>
       <c r="J8" t="n">
-        <v>621.6</v>
+        <v>577.5</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>81</v>
+        <v>112.5</v>
       </c>
       <c r="B9" t="n">
-        <v>123.2</v>
+        <v>110</v>
       </c>
       <c r="C9" t="n">
         <v>24</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>6462.545426230955</v>
+        <v>4989.715738556163</v>
       </c>
       <c r="F9" t="n">
-        <v>-79.60311452829683</v>
+        <v>-560.9580341702031</v>
       </c>
       <c r="G9" t="n">
         <v>700</v>
       </c>
       <c r="H9" t="n">
-        <v>6481.818152323912</v>
+        <v>4737.144673195204</v>
       </c>
       <c r="I9" t="n">
-        <v>42.08008903302414</v>
+        <v>48.80245728724617</v>
       </c>
       <c r="J9" t="n">
-        <v>695.1</v>
+        <v>523.6</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -802,34 +802,34 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="B11" t="n">
-        <v>95.2</v>
+        <v>116</v>
       </c>
       <c r="C11" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>6000</v>
+        <v>6435.513550672003</v>
       </c>
       <c r="F11" t="n">
-        <v>-334.4000000000001</v>
+        <v>-250.2756597831367</v>
       </c>
       <c r="G11" t="n">
         <v>700</v>
       </c>
       <c r="H11" t="n">
-        <v>6000</v>
+        <v>6489.952744506003</v>
       </c>
       <c r="I11" t="n">
-        <v>46.39999999999992</v>
+        <v>93.43988274397122</v>
       </c>
       <c r="J11" t="n">
-        <v>621.6</v>
+        <v>655.9</v>
       </c>
       <c r="K11" t="n">
         <v>2</v>
